--- a/data/fmsForecastOutput/File1/RPT_RPT3727870190544CM_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3727870190544CM_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1878,16 +1878,16 @@
         <v>422.708400261265</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>453.4289653891627</v>
+        <v>453.4289653891625</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>490.3488409442064</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>523.9056380931877</v>
+        <v>523.9056380931875</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>565.7411957771482</v>
+        <v>565.7411957771481</v>
       </c>
       <c r="H8" s="148" t="n">
         <v>43.80038879552758</v>
@@ -1899,10 +1899,10 @@
         <v>55.78413678070434</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>62.8553193567613</v>
+        <v>62.85531935676129</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>72.05343724877325</v>
+        <v>72.05343724877324</v>
       </c>
       <c r="M8" s="151" t="n">
         <v>54117487.22604285</v>
@@ -1914,10 +1914,10 @@
         <v>71086208.29719411</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>81159444.28729817</v>
+        <v>81159444.28729814</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>94564465.82708596</v>
+        <v>94564465.82708594</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1928,31 +1928,31 @@
         <v>513.9982774713776</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>551.3533845592119</v>
+        <v>551.3533845592117</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>596.2466311282914</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>637.0504947879019</v>
+        <v>637.0504947879017</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>687.921034794487</v>
+        <v>687.9210347944868</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>54.23146379455156</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>61.09161397144499</v>
+        <v>61.09161397144497</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>69.05488391573338</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>77.79843046522123</v>
+        <v>77.7984304652212</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>89.16988990886246</v>
+        <v>89.16988990886244</v>
       </c>
       <c r="AD8" s="151" t="n">
         <v>54117487.22604285</v>
@@ -1964,10 +1964,10 @@
         <v>71086208.29719411</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>81159444.28729817</v>
+        <v>81159444.28729814</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>94564465.82708596</v>
+        <v>94564465.82708594</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         <v>1466.597628378427</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1574.60167524626</v>
+        <v>1574.601675246259</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1695.393961657872</v>
+        <v>1695.393961657871</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>1789.993116722509</v>
@@ -2043,7 +2043,7 @@
         <v>109.555747592266</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>122.0031449042862</v>
+        <v>122.0031449042861</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>136.6232398648243</v>
@@ -2052,13 +2052,13 @@
         <v>155.8688220245749</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>27150333.6999508</v>
+        <v>27150333.69995079</v>
       </c>
       <c r="N9" s="159" t="n">
         <v>29777380.5793108</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>33379474.89299652</v>
+        <v>33379474.89299651</v>
       </c>
       <c r="P9" s="159" t="n">
         <v>37593461.83309863</v>
@@ -2078,7 +2078,7 @@
         <v>1595.718851827453</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1718.131098437191</v>
+        <v>1718.13109843719</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>1813.99893439639</v>
@@ -2102,13 +2102,13 @@
         <v>156.5307655939363</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>27150333.6999508</v>
+        <v>27150333.69995079</v>
       </c>
       <c r="AE9" s="159" t="n">
         <v>29777380.5793108</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>33379474.89299652</v>
+        <v>33379474.89299651</v>
       </c>
       <c r="AG9" s="159" t="n">
         <v>37593461.83309863</v>
@@ -2170,37 +2170,37 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>554.5851484458285</v>
+        <v>554.5851484458284</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>589.6705171895345</v>
+        <v>589.6705171895344</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>634.4364583789488</v>
+        <v>634.4364583789487</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>675.0609494533768</v>
+        <v>675.0609494533766</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>725.933697424749</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>53.98370778653291</v>
+        <v>53.9837077865329</v>
       </c>
       <c r="I10" s="162" t="n">
         <v>60.05617420664082</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>67.4884831092252</v>
+        <v>67.48848310922519</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>75.81398770652672</v>
+        <v>75.8139877065267</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>86.67670384981616</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>81267820.92599365</v>
+        <v>81267820.92599364</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>91767337.85418236</v>
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>657.7473465442785</v>
+        <v>657.7473465442782</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>700.0162969523204</v>
+        <v>700.0162969523203</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>753.4455524183281</v>
+        <v>753.445552418328</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>801.7190554933302</v>
+        <v>801.71905549333</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>862.1298323685046</v>
+        <v>862.1298323685045</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>64.1592647748259</v>
+        <v>64.15926477482589</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>71.39265721987168</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>80.24214381714222</v>
+        <v>80.24214381714221</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>90.15459800468879</v>
+        <v>90.15459800468876</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>103.0884958076134</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>81267820.92599365</v>
+        <v>81267820.92599364</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>91767337.85418236</v>
@@ -2360,7 +2360,7 @@
         <v>15409873.84807424</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>17947587.93403649</v>
+        <v>17947587.9340365</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>2061.843256475545</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>2237.832978250757</v>
+        <v>2237.832978250758</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>2397.549156854447</v>
@@ -2410,7 +2410,7 @@
         <v>15409873.84807424</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>17947587.93403649</v>
+        <v>17947587.9340365</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>596.5534293517519</v>
+        <v>596.5534293517517</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>634.6461063218512</v>
+        <v>634.6461063218511</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>683.4020695647991</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>727.7593080038673</v>
+        <v>727.7593080038672</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>783.0657078459391</v>
@@ -2485,13 +2485,13 @@
         <v>73.05254185152978</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>82.1303759636603</v>
+        <v>82.13037596366027</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>93.93500226074984</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91644669.60373859</v>
+        <v>91644669.60373858</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>103511277.3906772</v>
@@ -2511,37 +2511,37 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>710.6821106954368</v>
+        <v>710.6821106954366</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>756.7222879921242</v>
+        <v>756.7222879921238</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>815.1457969298913</v>
+        <v>815.1457969298912</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>868.0855194851914</v>
+        <v>868.0855194851912</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>934.0348403658028</v>
+        <v>934.0348403658026</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>69.28586404164732</v>
+        <v>69.2858640416473</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>77.11907085665004</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>86.74241682091802</v>
+        <v>86.74241682091801</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>97.53919911746614</v>
+        <v>97.53919911746611</v>
       </c>
       <c r="AC12" s="163" t="n">
         <v>111.5803077632288</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91644669.60373859</v>
+        <v>91644669.60373858</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>103511277.3906772</v>
@@ -2609,13 +2609,13 @@
         <v>1563.747862346919</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>1621.319610285061</v>
+        <v>1621.31961028506</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>1658.83533257231</v>
+        <v>1658.835332572309</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>1722.970589399678</v>
+        <v>1722.970589399677</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>1531.873884588692</v>
@@ -2630,22 +2630,22 @@
         <v>1573.312500371145</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>1640.497096024352</v>
+        <v>1640.497096024351</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.863287352</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>9094600.96585134</v>
+        <v>9094600.965851339</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>10671201.6267484</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>12494903.11074286</v>
+        <v>12494903.11074285</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>14909967.45920723</v>
+        <v>14909967.45920722</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2677,25 +2677,25 @@
         <v>1240.146584247042</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>1275.098196191383</v>
+        <v>1275.098196191382</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>1330.343972035406</v>
+        <v>1330.343972035405</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.863287352</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>9094600.96585134</v>
+        <v>9094600.965851339</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>10671201.6267484</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>12494903.11074286</v>
+        <v>12494903.11074285</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>14909967.45920723</v>
+        <v>14909967.45920722</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>629.3570556231881</v>
+        <v>629.357055623188</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>666.6356212146635</v>
+        <v>666.6356212146634</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>717.8634863755389</v>
+        <v>717.8634863755387</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>764.3085750219715</v>
+        <v>764.3085750219714</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>822.255144226933</v>
+        <v>822.2551442269329</v>
       </c>
       <c r="H14" s="167" t="n">
         <v>63.44836802871785</v>
@@ -2767,10 +2767,10 @@
         <v>70.39757635549209</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>79.32087532012584</v>
+        <v>79.32087532012582</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>89.34500574026526</v>
+        <v>89.34500574026524</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>102.3665296105765</v>
@@ -2799,16 +2799,16 @@
         <v>738.7135426668658</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>782.5009634380235</v>
+        <v>782.5009634380233</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>842.0363367652346</v>
+        <v>842.0363367652345</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>895.5294234894724</v>
+        <v>895.5294234894723</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>962.3440763524183</v>
+        <v>962.3440763524179</v>
       </c>
       <c r="Y14" s="167" t="n">
         <v>75.1855082346904</v>
@@ -2817,7 +2817,7 @@
         <v>83.42495941448634</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>93.99709531498209</v>
+        <v>93.99709531498208</v>
       </c>
       <c r="AB14" s="168" t="n">
         <v>105.8690272226929</v>
@@ -3214,7 +3214,7 @@
         <v>127398.7618741576</v>
       </c>
       <c r="X19" s="76" t="n">
-        <v>137464.128939358</v>
+        <v>137464.1289393581</v>
       </c>
       <c r="Y19" s="74" t="n">
         <v>892611.0383580375</v>
@@ -3348,7 +3348,7 @@
         <v>19427.78110666784</v>
       </c>
       <c r="W20" s="80" t="n">
-        <v>20724.08154176115</v>
+        <v>20724.08154176116</v>
       </c>
       <c r="X20" s="81" t="n">
         <v>22370.21468174311</v>
@@ -3412,7 +3412,7 @@
         <v>146538.0404681569</v>
       </c>
       <c r="D21" s="86" t="n">
-        <v>155624.7687124674</v>
+        <v>155624.7687124675</v>
       </c>
       <c r="E21" s="86" t="n">
         <v>164659.0163766933</v>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="T21" s="85" t="n">
-        <v>123554.7681841128</v>
+        <v>123554.7681841129</v>
       </c>
       <c r="U21" s="86" t="n">
         <v>131093.1449077861</v>
@@ -3471,7 +3471,7 @@
         <v>148122.8434159187</v>
       </c>
       <c r="X21" s="87" t="n">
-        <v>159834.3436211011</v>
+        <v>159834.3436211012</v>
       </c>
       <c r="Y21" s="85" t="n">
         <v>1143102.840989124</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>7085.533036943489</v>
+        <v>7085.53303694349</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>7476.015109537085</v>
+        <v>7476.015109537086</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>7892.439335118966</v>
+        <v>7892.439335118967</v>
       </c>
       <c r="F22" s="80" t="n">
         <v>8436.13602358095</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>5398.343515940877</v>
+        <v>5398.343515940878</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>5695.844967657503</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>158813.5503908115</v>
+        <v>158813.5503908116</v>
       </c>
       <c r="D25" s="92" t="n">
         <v>168916.6836769862</v>
@@ -4411,43 +4411,43 @@
         <v>434.4801059154825</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>476.8359053527951</v>
+        <v>476.8359053527949</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>518.9341468162563</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>561.4627213429644</v>
+        <v>561.4627213429642</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>607.8066610991845</v>
+        <v>607.8066610991843</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>45.02015467697814</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>51.89362239729681</v>
+        <v>51.8936223972968</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>59.03612083681868</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>67.3612118116795</v>
+        <v>67.36121181167948</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>77.41094239166497</v>
+        <v>77.41094239166496</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>55624566.64527631</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>65190006.93873837</v>
+        <v>65190006.93873836</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>75230239.72499706</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>86977499.64684275</v>
+        <v>86977499.64684272</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>101595769.6947172</v>
@@ -4461,43 +4461,43 @@
         <v>528.3122500004973</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>579.8153853492291</v>
+        <v>579.8153853492289</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>631.0053394249444</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>682.7185630952811</v>
+        <v>682.7185630952808</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>739.0711342559476</v>
+        <v>739.0711342559474</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>55.74171726619357</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>64.24528929803937</v>
+        <v>64.24528929803935</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>73.08049754803875</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>83.37554572650913</v>
+        <v>83.3755457265091</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>95.80008219418544</v>
+        <v>95.80008219418542</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>55624566.64527631</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>65190006.93873837</v>
+        <v>65190006.93873836</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>75230239.72499706</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>86977499.64684275</v>
+        <v>86977499.64684272</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>101595769.6947172</v>
@@ -4516,7 +4516,7 @@
         <v>1657.351073118176</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1795.876680632539</v>
+        <v>1795.876680632538</v>
       </c>
       <c r="F36" s="156" t="n">
         <v>1920.118085648131</v>
@@ -4540,13 +4540,13 @@
         <v>167.6207462228064</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>27923100.64133261</v>
+        <v>27923100.6413326</v>
       </c>
       <c r="N36" s="159" t="n">
         <v>31342259.08279359</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>35357811.76988092</v>
+        <v>35357811.76988091</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>40326348.34933034</v>
@@ -4575,7 +4575,7 @@
         <v>2078.349877256149</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>103.8963226318207</v>
+        <v>103.8963226318206</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>115.7890369759217</v>
@@ -4590,13 +4590,13 @@
         <v>168.3325978529948</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>27923100.64133261</v>
+        <v>27923100.6413326</v>
       </c>
       <c r="AE36" s="159" t="n">
         <v>31342259.08279359</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>35357811.76988092</v>
+        <v>35357811.76988091</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>40326348.34933034</v>
@@ -4612,37 +4612,37 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>570.1431998114102</v>
+        <v>570.1431998114101</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>620.2885750139499</v>
+        <v>620.2885750139498</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>671.618560151506</v>
+        <v>671.6185601515059</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>723.6695025403207</v>
+        <v>723.6695025403204</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>780.1474554163971</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>55.49813943152218</v>
+        <v>55.49813943152216</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>63.17453159601163</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>71.44374705142424</v>
+        <v>71.44374705142422</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>81.27306254880529</v>
+        <v>81.27306254880527</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>93.14984301210832</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>83547667.28660892</v>
+        <v>83547667.2866089</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>96532266.02153195</v>
@@ -4662,37 +4662,37 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>676.1994580582428</v>
+        <v>676.1994580582426</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>736.3639501473167</v>
+        <v>736.3639501473166</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>797.6023609373077</v>
+        <v>797.6023609373076</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>859.4477736206607</v>
+        <v>859.4477736206604</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>926.5149108615047</v>
+        <v>926.5149108615046</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>65.95915635097437</v>
+        <v>65.95915635097435</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>75.09965026645483</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>84.94485520526213</v>
+        <v>84.94485520526212</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>96.64628526150837</v>
+        <v>96.64628526150834</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>110.7872908673596</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>83547667.28660892</v>
+        <v>83547667.2866089</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>96532266.02153195</v>
@@ -4764,28 +4764,28 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1976.570575588811</v>
+        <v>1976.57057558881</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>2169.618965522412</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>2369.8283568883</v>
+        <v>2369.828356888301</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>2571.146373840159</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>2792.184239587262</v>
+        <v>2792.184239587263</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>190.3826721926081</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>217.422839395355</v>
+        <v>217.4228393953551</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>247.525521864773</v>
+        <v>247.5255218647731</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>283.6463642652209</v>
@@ -4816,37 +4816,37 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>613.3034929955603</v>
+        <v>613.3034929955601</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>667.6245002407297</v>
+        <v>667.6245002407296</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>723.4832799947479</v>
+        <v>723.4832799947478</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>780.1958994089556</v>
+        <v>780.1958994089555</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>841.5843802943906</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>60.0159178716395</v>
+        <v>60.01591787163949</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>68.33635548475814</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>77.33703912303852</v>
+        <v>77.33703912303851</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>88.0480425863864</v>
+        <v>88.04804258638639</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>100.9547856246037</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>94217874.2371383</v>
+        <v>94217874.23713829</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>108890079.2880371</v>
@@ -4855,7 +4855,7 @@
         <v>124838093.1462504</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>143829490.9230496</v>
+        <v>143829490.9230495</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>167384442.5250559</v>
@@ -4866,28 +4866,28 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>730.6366864282427</v>
+        <v>730.6366864282425</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>796.0441800702636</v>
+        <v>796.0441800702632</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>862.9537150982417</v>
+        <v>862.9537150982416</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>930.632910070647</v>
+        <v>930.6329100706467</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>1003.835469267256</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>71.23127676616213</v>
+        <v>71.23127676616211</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>81.12644295274342</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>91.82981883012701</v>
+        <v>91.829818830127</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>104.5671039121581</v>
@@ -4896,7 +4896,7 @@
         <v>119.9187286853443</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>94217874.2371383</v>
+        <v>94217874.23713829</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>108890079.2880371</v>
@@ -4905,7 +4905,7 @@
         <v>124838093.1462504</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>143829490.9230496</v>
+        <v>143829490.9230495</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>167384442.5250559</v>
@@ -4921,13 +4921,13 @@
         <v>1646.107819372303</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E40" s="156" t="n">
         <v>1717.863541306485</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665568</v>
       </c>
       <c r="G40" s="157" t="n">
         <v>1853.25437173247</v>
@@ -4936,22 +4936,22 @@
         <v>1575.67772535352</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>9574271.992684852</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="O40" s="159" t="n">
         <v>11306634.48479381</v>
@@ -4960,7 +4960,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>1454.660697278587</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>1514.639831400706</v>
+        <v>1514.639831400705</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>1278.83361453638</v>
@@ -4989,19 +4989,19 @@
         <v>1266.485950963122</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>1368.131111793329</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>9574271.992684852</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="AF40" s="159" t="n">
         <v>11306634.48479381</v>
@@ -5010,7 +5010,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>647.0552136023172</v>
+        <v>647.0552136023169</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>701.3182398682264</v>
+        <v>701.3182398682263</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>760.0192772073817</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>819.437827159598</v>
+        <v>819.4378271595978</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>883.7660707463903</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>65.23260041454256</v>
+        <v>65.23260041454255</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>74.0601053551034</v>
@@ -5044,7 +5044,7 @@
         <v>83.97891169062963</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>95.78942296867484</v>
+        <v>95.78942296867481</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>110.024323088838</v>
@@ -5070,22 +5070,22 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>759.4869158460933</v>
+        <v>759.4869158460932</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>823.2116330261814</v>
+        <v>823.2116330261811</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>891.4840498181826</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>960.1235795641902</v>
+        <v>960.12357956419</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1034.334718408665</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>77.2998008935072</v>
+        <v>77.29980089350718</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>87.76525561451476</v>
@@ -5374,7 +5374,7 @@
         <v>0.2938284664603</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.5058462103991553</v>
+        <v>0.5058462103991552</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.5743515682077862</v>
@@ -5383,7 +5383,7 @@
         <v>0.6469532886392041</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.7218229414437761</v>
+        <v>0.7218229414437759</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.03044604995358571</v>
@@ -5398,7 +5398,7 @@
         <v>0.07761790026602297</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.09193218454703324</v>
+        <v>0.09193218454703321</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>37617.55922164048</v>
@@ -5413,7 +5413,7 @@
         <v>100221.0428139322</v>
       </c>
       <c r="Q46" s="153" t="n">
-        <v>120653.7572106638</v>
+        <v>120653.7572106637</v>
       </c>
       <c r="S46" s="21" t="inlineStr">
         <is>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>0.357284893177672</v>
+        <v>0.3572848931776719</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.6150908774225641</v>
+        <v>0.615090877422564</v>
       </c>
       <c r="V46" s="149" t="n">
         <v>0.6983909393315143</v>
@@ -5433,7 +5433,7 @@
         <v>0.7866720314984609</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.8777108482161909</v>
+        <v>0.8777108482161905</v>
       </c>
       <c r="Y46" s="148" t="n">
         <v>0.03769678537450762</v>
@@ -5463,7 +5463,7 @@
         <v>100221.0428139322</v>
       </c>
       <c r="AH46" s="153" t="n">
-        <v>120653.7572106638</v>
+        <v>120653.7572106637</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" thickBot="1">
@@ -5476,13 +5476,13 @@
         <v>0.1600547166835736</v>
       </c>
       <c r="D47" s="156" t="n">
-        <v>0.3373613972721549</v>
+        <v>0.3373613972721548</v>
       </c>
       <c r="E47" s="156" t="n">
-        <v>0.3877024883220891</v>
+        <v>0.387702488322089</v>
       </c>
       <c r="F47" s="156" t="n">
-        <v>0.4346065578779158</v>
+        <v>0.4346065578779157</v>
       </c>
       <c r="G47" s="157" t="n">
         <v>0.4812619530017863</v>
@@ -5506,7 +5506,7 @@
         <v>2963.006951685063</v>
       </c>
       <c r="N47" s="159" t="n">
-        <v>6379.860301983938</v>
+        <v>6379.860301983939</v>
       </c>
       <c r="O47" s="159" t="n">
         <v>7633.214325149864</v>
@@ -5529,10 +5529,10 @@
         <v>0.3418857924318132</v>
       </c>
       <c r="V47" s="156" t="n">
-        <v>0.3929020140406079</v>
+        <v>0.3929020140406078</v>
       </c>
       <c r="W47" s="156" t="n">
-        <v>0.4404351198376363</v>
+        <v>0.4404351198376362</v>
       </c>
       <c r="X47" s="157" t="n">
         <v>0.4877162161993402</v>
@@ -5556,7 +5556,7 @@
         <v>2963.006951685063</v>
       </c>
       <c r="AE47" s="159" t="n">
-        <v>6379.860301983938</v>
+        <v>6379.860301983939</v>
       </c>
       <c r="AF47" s="159" t="n">
         <v>7633.214325149864</v>
@@ -5578,7 +5578,7 @@
         <v>0.2769285439035457</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.485372440217803</v>
+        <v>0.4853724402178028</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.5520338800525164</v>
@@ -5587,7 +5587,7 @@
         <v>0.6216016942617841</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.6930929696539324</v>
+        <v>0.6930929696539323</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.02695641892635234</v>
@@ -5602,7 +5602,7 @@
         <v>0.06981014565466857</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.08275551098426721</v>
+        <v>0.0827555109842672</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>40580.56617332555</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>0.3284419271691334</v>
+        <v>0.3284419271691333</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.5762007906777676</v>
+        <v>0.5762007906777675</v>
       </c>
       <c r="V48" s="162" t="n">
         <v>0.6555857032121692</v>
@@ -5637,7 +5637,7 @@
         <v>0.7382295237491442</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.8231276876432301</v>
+        <v>0.8231276876432297</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.03203751817337046</v>
@@ -5652,7 +5652,7 @@
         <v>0.08301509798571907</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.09842484506494795</v>
+        <v>0.09842484506494793</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>40580.56617332555</v>
@@ -5677,31 +5677,31 @@
         </is>
       </c>
       <c r="C49" s="155" t="n">
-        <v>0.4306827746401756</v>
+        <v>0.4306827746401755</v>
       </c>
       <c r="D49" s="156" t="n">
         <v>0.7620837373530948</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.8531117349636226</v>
+        <v>0.8531117349636225</v>
       </c>
       <c r="F49" s="156" t="n">
-        <v>0.9448874590390856</v>
+        <v>0.9448874590390854</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>1.042213721511509</v>
+        <v>1.042213721511508</v>
       </c>
       <c r="H49" s="155" t="n">
         <v>0.04733568736836367</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.08709167227941159</v>
+        <v>0.0870916722794116</v>
       </c>
       <c r="J49" s="156" t="n">
         <v>0.101548683497198</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.1186857196367911</v>
+        <v>0.118685719636791</v>
       </c>
       <c r="L49" s="157" t="n">
         <v>0.1385668765748691</v>
@@ -5716,10 +5716,10 @@
         <v>6733.132614278481</v>
       </c>
       <c r="P49" s="159" t="n">
-        <v>7971.199131429499</v>
+        <v>7971.199131429498</v>
       </c>
       <c r="Q49" s="160" t="n">
-        <v>9453.261256021153</v>
+        <v>9453.261256021151</v>
       </c>
       <c r="S49" s="32" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="T49" s="155" t="n">
-        <v>0.5652876700314217</v>
+        <v>0.5652876700314216</v>
       </c>
       <c r="U49" s="156" t="n">
         <v>1.000264151769451</v>
@@ -5745,13 +5745,13 @@
         <v>0.05444833516559641</v>
       </c>
       <c r="Z49" s="156" t="n">
-        <v>0.1002389246587058</v>
+        <v>0.1002389246587059</v>
       </c>
       <c r="AA49" s="156" t="n">
         <v>0.1169555994928261</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.1368177723837227</v>
+        <v>0.1368177723837226</v>
       </c>
       <c r="AC49" s="157" t="n">
         <v>0.1598997645271852</v>
@@ -5766,10 +5766,10 @@
         <v>6733.132614278481</v>
       </c>
       <c r="AG49" s="159" t="n">
-        <v>7971.199131429499</v>
+        <v>7971.199131429498</v>
       </c>
       <c r="AH49" s="160" t="n">
-        <v>9453.261256021153</v>
+        <v>9453.261256021151</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickTop="1">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.2840201032039681</v>
+        <v>0.284020103203968</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.4980559956850818</v>
+        <v>0.4980559956850817</v>
       </c>
       <c r="E50" s="162" t="n">
         <v>0.5658050690305007</v>
@@ -5791,7 +5791,7 @@
         <v>0.6363957031580589</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.7090144378704674</v>
+        <v>0.7090144378704671</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.02779329872153087</v>
@@ -5806,7 +5806,7 @@
         <v>0.07181964941869433</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.08505195944216959</v>
+        <v>0.08505195944216956</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>43632.183201481</v>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.3383569626684924</v>
+        <v>0.3383569626684923</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.5938586384580706</v>
+        <v>0.5938586384580704</v>
       </c>
       <c r="V50" s="162" t="n">
         <v>0.6748788808842024</v>
@@ -5841,7 +5841,7 @@
         <v>0.7591052268220134</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.8457070468774527</v>
+        <v>0.8457070468774524</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.03298711781284806</v>
@@ -5856,7 +5856,7 @@
         <v>0.08529403406476792</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.10102862172803</v>
+        <v>0.1010286217280299</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>43632.183201481</v>
@@ -5995,7 +5995,7 @@
         <v>0.6114140734413246</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.6794520036801071</v>
+        <v>0.6794520036801069</v>
       </c>
       <c r="H52" s="179" t="n">
         <v>0.02769763832055317</v>
@@ -6010,7 +6010,7 @@
         <v>0.07147217195584095</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.08458827426258014</v>
+        <v>0.08458827426258013</v>
       </c>
       <c r="M52" s="182" t="n">
         <v>43632.183201481</v>
@@ -6036,7 +6036,7 @@
         <v>0.3224767029156768</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.5644923218958643</v>
+        <v>0.5644923218958641</v>
       </c>
       <c r="V52" s="186" t="n">
         <v>0.6392904420103169</v>
@@ -6045,7 +6045,7 @@
         <v>0.7163851232292131</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.7952113349465075</v>
+        <v>0.7952113349465073</v>
       </c>
       <c r="Y52" s="185" t="n">
         <v>0.03282134873963769</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.008277563575957781</v>
+        <v>0.00827756357595778</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.007681120878381053</v>
+        <v>0.007681120878381052</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0.007176269940001829</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01006522088766731</v>
+        <v>0.0100652208876673</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009339967926109558</v>
+        <v>0.009339967926109556</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0.008726087263822402</v>
@@ -6541,7 +6541,7 @@
         <v>0.007231841349992076</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006747734060421263</v>
+        <v>0.006747734060421262</v>
       </c>
       <c r="E59" s="162" t="n">
         <v>0.00631820112585564</v>
@@ -6591,7 +6591,7 @@
         <v>0.008577085902708975</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008010445956003058</v>
+        <v>0.008010445956003056</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0.007503384262820858</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.006898289345998357</v>
+        <v>0.006898289345998356</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006438439643750032</v>
+        <v>0.006438439643750031</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.00602920895892672</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008218024725680104</v>
+        <v>0.008218024725680102</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007676893830727928</v>
+        <v>0.007676893830727925</v>
       </c>
       <c r="V61" s="162" t="n">
         <v>0.007191497597908807</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006672855419431155</v>
+        <v>0.006672855419431154</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006216760414823188</v>
+        <v>0.006216760414823187</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.005807680867221493</v>
@@ -6999,7 +6999,7 @@
         <v>0.00783232446915332</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.007297271341724557</v>
+        <v>0.007297271341724554</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0.006812267813240547</v>
@@ -7300,7 +7300,7 @@
         <v>0.003513344942360763</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005148577945557916</v>
+        <v>0.005148577945557915</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.00687361950276794</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004272101636542019</v>
+        <v>0.004272101636542018</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006260486410509579</v>
+        <v>0.006260486410509578</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.008358075170100041</v>
@@ -7359,7 +7359,7 @@
         <v>0.01034979895088289</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01229713828036028</v>
+        <v>0.01229713828036027</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>0.0004507453339504126</v>
@@ -7504,7 +7504,7 @@
         <v>0.003069496597374088</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004522938164370782</v>
+        <v>0.004522938164370781</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>0.006051738694918801</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003640474772552817</v>
+        <v>0.003640474772552816</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.00536932122748387</v>
+        <v>0.005369321227483869</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>0.00718693817775678</v>
@@ -7606,7 +7606,7 @@
         <v>0.01067464507930155</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01600814238315599</v>
+        <v>0.01600814238315598</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.02175241004797995</v>
@@ -7621,13 +7621,13 @@
         <v>0.001173233971719017</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001829426114088588</v>
+        <v>0.001829426114088587</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.002589260600614968</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003443865073796661</v>
+        <v>0.003443865073796662</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.004410270034119569</v>
@@ -7636,13 +7636,13 @@
         <v>75.63555036703737</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>119.6771143320952</v>
+        <v>119.6771143320951</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>171.679576696314</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>231.2977026134039</v>
+        <v>231.297702613404</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>300.8759082449787</v>
@@ -7656,7 +7656,7 @@
         <v>0.01401088132752049</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.02101130122249695</v>
+        <v>0.02101130122249693</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>0.02855087298038324</v>
@@ -7671,13 +7671,13 @@
         <v>0.001349523796342184</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.002105594043830822</v>
+        <v>0.002105594043830821</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>0.002982101937308073</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003969996973763164</v>
+        <v>0.003969996973763165</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>0.005089247570475422</v>
@@ -7686,13 +7686,13 @@
         <v>75.63555036703737</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>119.6771143320952</v>
+        <v>119.6771143320951</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>171.679576696314</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>231.2977026134039</v>
+        <v>231.297702613404</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>300.8759082449787</v>
@@ -7708,7 +7708,7 @@
         <v>0.003420266531896986</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005049382969010482</v>
+        <v>0.005049382969010481</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.0067698815564988</v>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004074609445579534</v>
+        <v>0.004074609445579533</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006020647720353812</v>
+        <v>0.006020647720353809</v>
       </c>
       <c r="V72" s="162" t="n">
         <v>0.008074954323751774</v>
@@ -7962,7 +7962,7 @@
         <v>0.003883373964929843</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005722926620725622</v>
+        <v>0.005722926620725619</v>
       </c>
       <c r="V74" s="186" t="n">
         <v>0.007649137148996285</v>
@@ -8263,43 +8263,43 @@
         <v>434.7857252904611</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>477.3545812620181</v>
+        <v>477.354581262018</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>519.522548273907</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>562.1184507679147</v>
+        <v>562.1184507679145</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>608.5385971166405</v>
+        <v>608.5385971166404</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>45.05182248258416</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>51.95006942965668</v>
+        <v>51.95006942965667</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>59.10305984973107</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>67.43988262455123</v>
+        <v>67.43988262455122</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>77.50416258898761</v>
+        <v>77.5041625889876</v>
       </c>
       <c r="M79" s="151" t="n">
         <v>55663693.74237496</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>65260917.0479429</v>
+        <v>65260917.04794289</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>75315540.68849149</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>87079080.22140096</v>
+        <v>87079080.22140093</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>101718113.86733</v>
@@ -8310,46 +8310,46 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>528.6838722161992</v>
+        <v>528.6838722161991</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>580.4460766809882</v>
+        <v>580.446076680988</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>631.7208145267098</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>683.5159065942591</v>
+        <v>683.5159065942589</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>739.9611422424441</v>
+        <v>739.9611422424439</v>
       </c>
       <c r="Y79" s="148" t="n">
         <v>55.78092676867524</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>64.31517179527981</v>
+        <v>64.3151717952798</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>73.16336099332734</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>83.47291959760673</v>
+        <v>83.4729195976067</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>95.91544705462702</v>
+        <v>95.91544705462701</v>
       </c>
       <c r="AD79" s="151" t="n">
         <v>55663693.74237496</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>65260917.0479429</v>
+        <v>65260917.04794289</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>75315540.68849149</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>87079080.22140096</v>
+        <v>87079080.22140093</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>101718113.86733</v>
@@ -8368,7 +8368,7 @@
         <v>1657.688434515448</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1796.264383120861</v>
+        <v>1796.26438312086</v>
       </c>
       <c r="F80" s="156" t="n">
         <v>1920.552692206009</v>
@@ -8418,7 +8418,7 @@
         <v>1679.919897836348</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1820.354305519133</v>
+        <v>1820.354305519132</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1946.309460392133</v>
@@ -8427,7 +8427,7 @@
         <v>2078.837593472348</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>103.9073473933673</v>
+        <v>103.9073473933672</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>115.8126063644095</v>
@@ -8467,13 +8467,13 @@
         <v>570.4304296932611</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>620.7852181263925</v>
+        <v>620.7852181263924</v>
       </c>
       <c r="E81" s="162" t="n">
         <v>672.1829639713793</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>724.2988326078922</v>
+        <v>724.298832607892</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>780.8494536669408</v>
@@ -8488,7 +8488,7 @@
         <v>71.50378577896147</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>81.34374064393855</v>
+        <v>81.34374064393853</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>93.23366181633428</v>
@@ -8514,19 +8514,19 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>676.5401175460871</v>
+        <v>676.540117546087</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>736.953530705178</v>
+        <v>736.9535307051779</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>798.2726369629606</v>
+        <v>798.2726369629605</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>860.1951815514194</v>
+        <v>860.1951815514192</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>927.348614595346</v>
+        <v>927.3486145953459</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>65.99238561809874</v>
@@ -8535,10 +8535,10 @@
         <v>75.15977989894216</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>85.01623977323122</v>
+        <v>85.01623977323121</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>96.73033248613321</v>
+        <v>96.73033248613319</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>110.8869803348204</v>
@@ -8578,7 +8578,7 @@
         <v>1959.883692900946</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>2128.391651352345</v>
+        <v>2128.391651352346</v>
       </c>
       <c r="H82" s="155" t="n">
         <v>165.5612766460949</v>
@@ -8587,7 +8587,7 @@
         <v>188.9947652018878</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>215.0223717552665</v>
+        <v>215.0223717552666</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>246.1776842005249</v>
@@ -8602,7 +8602,7 @@
         <v>12363630.29315462</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>14256946.4635634</v>
+        <v>14256946.46356341</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>16533845.42371053</v>
@@ -8616,13 +8616,13 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1977.14987414017</v>
+        <v>1977.149874140169</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>2170.640240975404</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>2370.976649653296</v>
+        <v>2370.976649653297</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>2572.422561404213</v>
@@ -8634,7 +8634,7 @@
         <v>190.4384700515701</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>217.5251839140575</v>
+        <v>217.5251839140576</v>
       </c>
       <c r="AA82" s="156" t="n">
         <v>247.6454595662032</v>
@@ -8643,7 +8643,7 @@
         <v>283.7871520345784</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>326.5446585939129</v>
+        <v>326.544658593913</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>10673334.20310791</v>
@@ -8652,7 +8652,7 @@
         <v>12363630.29315462</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>14256946.4635634</v>
+        <v>14256946.46356341</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>16533845.42371053</v>
@@ -8668,22 +8668,22 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>613.5978316546423</v>
+        <v>613.5978316546421</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>668.1340440590276</v>
+        <v>668.1340440590275</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>724.0618841542939</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>780.8409244870991</v>
+        <v>780.8409244870988</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>842.3034066523544</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>60.04472091123028</v>
+        <v>60.04472091123026</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>68.38851110141049</v>
@@ -8692,13 +8692,13 @@
         <v>77.39888924972546</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>88.12083609323858</v>
+        <v>88.12083609323855</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>101.0410385940341</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>94263091.59376717</v>
+        <v>94263091.59376715</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>108973186.2841931</v>
@@ -8718,28 +8718,28 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>730.9873360250825</v>
+        <v>730.9873360250823</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>796.6517362502727</v>
+        <v>796.6517362502724</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>863.6438604310476</v>
+        <v>863.6438604310475</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>931.4023085845279</v>
+        <v>931.4023085845276</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>1004.693118456526</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>71.26546231822158</v>
+        <v>71.26546231822157</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>81.18836020936321</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>91.90325952546119</v>
+        <v>91.90325952546118</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>104.6535545131204</v>
@@ -8748,7 +8748,7 @@
         <v>120.0211839218687</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>94263091.59376717</v>
+        <v>94263091.59376715</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>108973186.2841931</v>
@@ -8773,13 +8773,13 @@
         <v>1646.107819372303</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E84" s="156" t="n">
         <v>1717.863541306485</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665568</v>
       </c>
       <c r="G84" s="157" t="n">
         <v>1853.25437173247</v>
@@ -8788,22 +8788,22 @@
         <v>1575.67772535352</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>9574271.992684852</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="O84" s="159" t="n">
         <v>11306634.48479381</v>
@@ -8812,7 +8812,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>1454.660697278587</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>1514.639831400706</v>
+        <v>1514.639831400705</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>1278.83361453638</v>
@@ -8841,19 +8841,19 @@
         <v>1266.485950963122</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>1368.131111793329</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>9574271.992684852</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="AF84" s="159" t="n">
         <v>11306634.48479381</v>
@@ -8862,7 +8862,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,31 +8872,31 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>647.3399333665791</v>
+        <v>647.3399333665789</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>701.8102397959243</v>
+        <v>701.8102397959242</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>760.5766220149648</v>
+        <v>760.5766220149645</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>820.0575318630433</v>
+        <v>820.0575318630432</v>
       </c>
       <c r="G85" s="181" t="n">
         <v>884.4551172220653</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>65.26130431835445</v>
+        <v>65.26130431835443</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>74.11206117830693</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>84.04049593168891</v>
+        <v>84.04049593168889</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>95.86186428635207</v>
+        <v>95.86186428635204</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>110.1101058254381</v>
@@ -8922,28 +8922,28 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>759.8211082474431</v>
+        <v>759.821108247443</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>823.7891455460398</v>
+        <v>823.7891455460394</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>892.1378016651554</v>
+        <v>892.1378016651552</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>960.8496786999931</v>
+        <v>960.8496786999929</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1035.14115884124</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>77.33381465404142</v>
+        <v>77.3338146540414</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>87.82682609273994</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>99.5899562949603</v>
+        <v>99.58995629496029</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>113.5911541519564</v>
@@ -9343,7 +9343,7 @@
         <v>127398.7618741576</v>
       </c>
       <c r="X90" s="76" t="n">
-        <v>137464.128939358</v>
+        <v>137464.1289393581</v>
       </c>
       <c r="Y90" s="74" t="n">
         <v>892611.0383580375</v>
@@ -9463,7 +9463,7 @@
         <v>19427.78110666784</v>
       </c>
       <c r="W91" s="80" t="n">
-        <v>20724.08154176115</v>
+        <v>20724.08154176116</v>
       </c>
       <c r="X91" s="81" t="n">
         <v>22370.21468174311</v>
@@ -9527,7 +9527,7 @@
         <v>146538.0404681569</v>
       </c>
       <c r="D92" s="86" t="n">
-        <v>155624.7687124674</v>
+        <v>155624.7687124675</v>
       </c>
       <c r="E92" s="86" t="n">
         <v>164659.0163766933</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="T92" s="85" t="n">
-        <v>123554.7681841128</v>
+        <v>123554.7681841129</v>
       </c>
       <c r="U92" s="86" t="n">
         <v>131093.1449077861</v>
@@ -9586,7 +9586,7 @@
         <v>148122.8434159187</v>
       </c>
       <c r="X92" s="87" t="n">
-        <v>159834.3436211011</v>
+        <v>159834.3436211012</v>
       </c>
       <c r="Y92" s="85" t="n">
         <v>1143102.840989124</v>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>7085.533036943489</v>
+        <v>7085.53303694349</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>7476.015109537085</v>
+        <v>7476.015109537086</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>7892.439335118966</v>
+        <v>7892.439335118967</v>
       </c>
       <c r="F93" s="80" t="n">
         <v>8436.13602358095</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>5398.343515940877</v>
+        <v>5398.343515940878</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>5695.844967657503</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>158813.5503908115</v>
+        <v>158813.5503908116</v>
       </c>
       <c r="D96" s="133" t="n">
         <v>168916.6836769862</v>
